--- a/Notes/notes-WILD_johto.xlsx
+++ b/Notes/notes-WILD_johto.xlsx
@@ -1045,7 +1045,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1148,6 +1148,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Notes/notes-WILD_johto.xlsx
+++ b/Notes/notes-WILD_johto.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="277">
   <si>
     <t>RATTATA</t>
   </si>
@@ -826,6 +826,12 @@
   <si>
     <t>same</t>
   </si>
+  <si>
+    <t>CATERPIE WEEDLE</t>
+  </si>
+  <si>
+    <t>EEVEE</t>
+  </si>
 </sst>
 </file>
 

--- a/Notes/notes-WILD_johto.xlsx
+++ b/Notes/notes-WILD_johto.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="274">
   <si>
     <t>RATTATA</t>
   </si>
@@ -805,6 +805,27 @@
   <si>
     <t>DEWGONG</t>
   </si>
+  <si>
+    <t>HERACROSS</t>
+  </si>
+  <si>
+    <t>SCYTHER</t>
+  </si>
+  <si>
+    <t>PINSIR</t>
+  </si>
+  <si>
+    <t>METAPOD
+KAKUNA</t>
+  </si>
+  <si>
+    <t>LEDYBA
+SPINARAK</t>
+  </si>
+  <si>
+    <t>BUTTERFREE
+BEEDRILL</t>
+  </si>
 </sst>
 </file>
 
@@ -1140,7 +1161,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{F196C564-2C88-4BED-88CA-3DF8249174BB}"/>
   </cellStyles>
-  <dxfs count="1699">
+  <dxfs count="1725">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -8508,6 +8529,266 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -19109,90 +19390,90 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A13:A14">
-    <cfRule type="cellIs" dxfId="1698" priority="27" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1724" priority="27" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="1697" priority="25" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1723" priority="25" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:L13">
-    <cfRule type="cellIs" dxfId="1696" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1722" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:L18">
-    <cfRule type="cellIs" dxfId="1695" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1721" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2 A2">
-    <cfRule type="duplicateValues" dxfId="1694" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="1720" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2 A2:A11">
-    <cfRule type="duplicateValues" dxfId="1693" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1719" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3 A3">
-    <cfRule type="duplicateValues" dxfId="1692" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="1718" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4 A4">
-    <cfRule type="duplicateValues" dxfId="1691" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1717" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5 A5">
-    <cfRule type="duplicateValues" dxfId="1690" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1716" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6 A6">
-    <cfRule type="duplicateValues" dxfId="1689" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1715" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7 A7">
-    <cfRule type="duplicateValues" dxfId="1688" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="1714" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8 A8">
-    <cfRule type="duplicateValues" dxfId="1687" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="1713" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9 A9">
-    <cfRule type="duplicateValues" dxfId="1686" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="1712" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10 A10">
-    <cfRule type="duplicateValues" dxfId="1685" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1711" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N11 A11">
-    <cfRule type="duplicateValues" dxfId="1684" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1710" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20 A20">
-    <cfRule type="duplicateValues" dxfId="1683" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1709" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20 A20:A29">
-    <cfRule type="duplicateValues" dxfId="1682" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1708" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21 A21">
-    <cfRule type="duplicateValues" dxfId="1681" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1707" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22 A22">
-    <cfRule type="duplicateValues" dxfId="1680" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1706" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23 A23">
-    <cfRule type="duplicateValues" dxfId="1679" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="1705" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24 A24">
-    <cfRule type="duplicateValues" dxfId="1678" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1704" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25 A25">
-    <cfRule type="duplicateValues" dxfId="1677" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1703" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26 A26">
-    <cfRule type="duplicateValues" dxfId="1676" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1702" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N27 A27">
-    <cfRule type="duplicateValues" dxfId="1675" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1701" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N28 A28">
-    <cfRule type="duplicateValues" dxfId="1674" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1700" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N29 A29">
-    <cfRule type="duplicateValues" dxfId="1673" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1699" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20365,108 +20646,108 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2 N2">
-    <cfRule type="duplicateValues" dxfId="1672" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="1698" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A11 N2:N11">
-    <cfRule type="duplicateValues" dxfId="1671" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="1697" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3 N3">
-    <cfRule type="duplicateValues" dxfId="1670" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1696" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4 N4">
-    <cfRule type="duplicateValues" dxfId="1669" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="1695" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5 N5">
-    <cfRule type="duplicateValues" dxfId="1668" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="1694" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6 N6">
-    <cfRule type="duplicateValues" dxfId="1667" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="1693" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7 N7">
-    <cfRule type="duplicateValues" dxfId="1666" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1692" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8 N8">
-    <cfRule type="duplicateValues" dxfId="1665" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="1691" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9 N9">
-    <cfRule type="duplicateValues" dxfId="1664" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1690" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10 N10">
-    <cfRule type="duplicateValues" dxfId="1663" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="1689" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11 N11">
-    <cfRule type="duplicateValues" dxfId="1662" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1688" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A14">
-    <cfRule type="cellIs" dxfId="1661" priority="56" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1687" priority="56" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="1660" priority="55" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1686" priority="55" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20 N20">
-    <cfRule type="duplicateValues" dxfId="1659" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1685" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A29 N20:N29">
-    <cfRule type="duplicateValues" dxfId="1658" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="1684" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21 N21">
-    <cfRule type="duplicateValues" dxfId="1657" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="1683" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22 N22">
-    <cfRule type="duplicateValues" dxfId="1656" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1682" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23 N23">
-    <cfRule type="duplicateValues" dxfId="1655" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="1681" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24 N24">
-    <cfRule type="duplicateValues" dxfId="1654" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="1680" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25 N25">
-    <cfRule type="duplicateValues" dxfId="1653" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="1679" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26 N26">
-    <cfRule type="duplicateValues" dxfId="1652" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1678" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27 N27">
-    <cfRule type="duplicateValues" dxfId="1651" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="1677" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28 N28">
-    <cfRule type="duplicateValues" dxfId="1650" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1676" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29 N29">
-    <cfRule type="duplicateValues" dxfId="1649" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="1675" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:L13">
-    <cfRule type="cellIs" dxfId="1648" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="1674" priority="32" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:L18">
-    <cfRule type="cellIs" dxfId="1647" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="1673" priority="31" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13:N14">
-    <cfRule type="cellIs" dxfId="1646" priority="4" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1672" priority="4" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N17:N18">
-    <cfRule type="cellIs" dxfId="1645" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1671" priority="3" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:AA13">
-    <cfRule type="cellIs" dxfId="1644" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1670" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18:AA18">
-    <cfRule type="cellIs" dxfId="1643" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1669" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21649,174 +21930,174 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="1642" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="1668" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A11">
-    <cfRule type="duplicateValues" dxfId="1641" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="1667" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="1640" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="1666" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="1639" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="1665" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="1638" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1664" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="1637" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="1663" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="1636" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="1662" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="1635" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="1661" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="1634" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="1660" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" dxfId="1633" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="1659" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="1632" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="1658" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A14">
-    <cfRule type="cellIs" dxfId="1631" priority="53" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1657" priority="53" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="1630" priority="51" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1656" priority="51" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="duplicateValues" dxfId="1629" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="1655" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A29">
-    <cfRule type="duplicateValues" dxfId="1628" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="1654" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21">
-    <cfRule type="duplicateValues" dxfId="1627" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="1653" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="1626" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="1652" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="1625" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="1651" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24">
-    <cfRule type="duplicateValues" dxfId="1624" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="1650" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="1623" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="1649" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="1622" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1648" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
-    <cfRule type="duplicateValues" dxfId="1621" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="1647" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="duplicateValues" dxfId="1620" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="1646" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29">
-    <cfRule type="duplicateValues" dxfId="1619" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="1645" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:L13">
-    <cfRule type="cellIs" dxfId="1618" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="1644" priority="28" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:L18">
-    <cfRule type="cellIs" dxfId="1617" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="1643" priority="27" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2">
-    <cfRule type="duplicateValues" dxfId="1616" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="1642" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N11">
-    <cfRule type="duplicateValues" dxfId="1615" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1641" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3">
-    <cfRule type="duplicateValues" dxfId="1614" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="1640" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4">
-    <cfRule type="duplicateValues" dxfId="1613" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1639" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5">
-    <cfRule type="duplicateValues" dxfId="1612" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="1638" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6">
-    <cfRule type="duplicateValues" dxfId="1611" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1637" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7">
-    <cfRule type="duplicateValues" dxfId="1610" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="1636" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8">
-    <cfRule type="duplicateValues" dxfId="1609" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="1635" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N9">
-    <cfRule type="duplicateValues" dxfId="1608" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="1634" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N10">
-    <cfRule type="duplicateValues" dxfId="1607" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1633" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N11">
-    <cfRule type="duplicateValues" dxfId="1606" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1632" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N13:N14">
-    <cfRule type="cellIs" dxfId="1605" priority="26" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1631" priority="26" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N17:N18">
-    <cfRule type="cellIs" dxfId="1604" priority="25" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1630" priority="25" operator="notEqual">
       <formula>100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20">
-    <cfRule type="duplicateValues" dxfId="1603" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1629" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:N29">
-    <cfRule type="duplicateValues" dxfId="1602" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1628" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21">
-    <cfRule type="duplicateValues" dxfId="1601" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1627" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22">
-    <cfRule type="duplicateValues" dxfId="1600" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1626" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N23">
-    <cfRule type="duplicateValues" dxfId="1599" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="1625" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="duplicateValues" dxfId="1598" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1624" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="duplicateValues" dxfId="1597" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1623" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="duplicateValues" dxfId="1596" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1622" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N27">
-    <cfRule type="duplicateValues" dxfId="1595" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1621" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N28">
-    <cfRule type="duplicateValues" dxfId="1594" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1620" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N29">
-    <cfRule type="duplicateValues" dxfId="1593" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1619" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P13:Y13">
-    <cfRule type="cellIs" dxfId="1592" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1618" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P18:Y18">
-    <cfRule type="cellIs" dxfId="1591" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1617" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21824,7 +22105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A24681B6-27E1-4272-A52D-3D9E00E1FCD9}">
   <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22624,7 +22905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C3149D4-8673-4BC0-B619-9E2F95A2B206}">
   <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -23443,7 +23724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ECCE3A5-7C17-4A69-876A-DCC2B76840C3}">
   <dimension ref="A1:Z30"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -24222,7 +24503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57BB131-FE49-42CB-8F82-928765832F30}">
   <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -25059,7 +25340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75AD882F-97F3-4B83-BD65-84D8D599A927}">
   <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -25900,7 +26181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D8D2B9-E2BA-4C95-8DBA-5AEDF86748D1}">
   <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -26734,7 +27015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF1576D-D7FC-41E4-BF02-05DF4184BEDE}">
   <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -27522,7 +27803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2408D079-F1AB-4918-96CD-EC5E5C396DAB}">
   <dimension ref="A1:AC313"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -31815,7 +32096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A9CFB9-883B-4258-A7F2-A695B364A020}">
   <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
